--- a/GourmetProject/GameConfig/Datas/reward_pool.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward_pool.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,73 +456,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奖励池ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>奖励池类型</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>特殊标签筛选</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>品质权重配置</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>是否允许兜底</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>与当前进度的隐藏分下限距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>RewardPoolKind</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pool_dish</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dish</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pool_fragment</t>
+          <t>pool_dish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fragment</t>
+          <t>Dish</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -540,20 +554,16 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pool_passive</t>
+          <t>pool_fragment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PassiveItem</t>
+          <t>Fragment</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Common:65|Uncommon:30|Rare:5</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>true</t>
@@ -567,7 +577,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pool_passive_boss</t>
+          <t>pool_passive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,14 +585,10 @@
           <t>PassiveItem</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BossReward|ScoreBuild</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Common:35|Uncommon:40|Rare:20|Epic:5</t>
+          <t>Common:65|Uncommon:30|Rare:5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -598,26 +604,57 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
+          <t>pool_passive_boss</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PassiveItem</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BossReward|ScoreBuild</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Common:35|Uncommon:40|Rare:20|Epic:5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>pool_active</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ActiveItem</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Common:80|Uncommon:20</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>
